--- a/data/trans_bre/IP1006-Edad-trans_bre.xlsx
+++ b/data/trans_bre/IP1006-Edad-trans_bre.xlsx
@@ -639,12 +639,12 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,04; 0,0</t>
+          <t>-2,64; 0,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-4,14; 0,0</t>
+          <t>-2,59; 0,0</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -714,17 +714,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-0,6; 0,97</t>
+          <t>-0,81; 1,03</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-2,68; -0,26</t>
+          <t>-2,58; -0,25</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-1,2; 0,53</t>
+          <t>-0,99; 0,52</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -794,17 +794,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,56; 0,0</t>
+          <t>-2,54; 0,0</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,46</t>
+          <t>0,0; 2,15</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,58</t>
+          <t>0,0; 1,59</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -874,17 +874,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-0,66; 2,07</t>
+          <t>-0,66; 1,73</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-3,44; 0,39</t>
+          <t>-3,38; 0,39</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,18</t>
+          <t>0,0; 2,84</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -954,27 +954,27 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,4; 0,56</t>
+          <t>-0,41; 0,54</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,3; -0,07</t>
+          <t>-1,23; -0,04</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,35; 0,66</t>
+          <t>-0,33; 0,59</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 17,22</t>
+          <t>-100,0; 72,12</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">

--- a/data/trans_bre/IP1006-Edad-trans_bre.xlsx
+++ b/data/trans_bre/IP1006-Edad-trans_bre.xlsx
@@ -639,12 +639,12 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,64; 0,0</t>
+          <t>-2,01; 0,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-2,59; 0,0</t>
+          <t>-3,01; 0,0</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -714,12 +714,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-0,81; 1,03</t>
+          <t>-0,81; 0,95</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-2,58; -0,25</t>
+          <t>-2,56; -0,25</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -794,17 +794,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,54; 0,0</t>
+          <t>-2,2; 0,0</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,15</t>
+          <t>0,0; 2,22</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,59</t>
+          <t>0,0; 1,81</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -874,17 +874,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-0,66; 1,73</t>
+          <t>-0,67; 1,92</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-3,38; 0,39</t>
+          <t>-3,52; 0,39</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,84</t>
+          <t>0,0; 3,37</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -954,17 +954,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,41; 0,54</t>
+          <t>-0,39; 0,58</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,23; -0,04</t>
+          <t>-1,29; -0,09</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,33; 0,59</t>
+          <t>-0,38; 0,63</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -974,7 +974,7 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 72,12</t>
+          <t>-100,0; 63,0</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">

--- a/data/trans_bre/IP1006-Edad-trans_bre.xlsx
+++ b/data/trans_bre/IP1006-Edad-trans_bre.xlsx
@@ -639,12 +639,12 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,01; 0,0</t>
+          <t>-2,04; 0,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-3,01; 0,0</t>
+          <t>-4,14; 0,0</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -714,17 +714,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-0,81; 0,95</t>
+          <t>-0,6; 0,97</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-2,56; -0,25</t>
+          <t>-2,68; -0,26</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-0,99; 0,52</t>
+          <t>-1,2; 0,53</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -794,17 +794,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,2; 0,0</t>
+          <t>-2,56; 0,0</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,22</t>
+          <t>0,0; 2,46</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,81</t>
+          <t>0,0; 1,58</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -874,17 +874,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-0,67; 1,92</t>
+          <t>-0,66; 2,07</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-3,52; 0,39</t>
+          <t>-3,44; 0,39</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,37</t>
+          <t>0,0; 3,18</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -954,27 +954,27 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,39; 0,58</t>
+          <t>-0,4; 0,56</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,29; -0,09</t>
+          <t>-1,3; -0,07</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,38; 0,63</t>
+          <t>-0,35; 0,66</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; —</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 63,0</t>
+          <t>-100,0; 17,22</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">

--- a/data/trans_bre/IP1006-Edad-trans_bre.xlsx
+++ b/data/trans_bre/IP1006-Edad-trans_bre.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +141,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H14"/>
+  <dimension ref="A1:H19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -594,239 +603,133 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>-0,4</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>-0,6</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>-0.403918712049319</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>-0.5956566421311512</v>
+      </c>
+      <c r="F4" s="6" t="inlineStr"/>
+      <c r="G4" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>-2,04; 0,0</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>-4,14; 0,0</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr"/>
+      <c r="D5" s="5" t="n">
+        <v>-2.038985595476226</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>-4.139936282467389</v>
+      </c>
+      <c r="F5" s="6" t="inlineStr"/>
+      <c r="G5" s="6" t="inlineStr"/>
+      <c r="H5" s="6" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr"/>
+      <c r="D6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="6" t="inlineStr"/>
+      <c r="G6" s="6" t="inlineStr"/>
+      <c r="H6" s="6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>3-7</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>0,19</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>-1,05</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-0,23</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>70,48%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>-47,85%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>-0,6; 0,97</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>-2,68; -0,26</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>-1,2; 0,53</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>0.1902784759623697</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>-1.051905068008904</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>-0.233519424035343</v>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>0.7048135933693279</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>-0.4784806697583454</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>8-11</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>-0,51</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>0,44</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>0,32</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>-0.5999419171392142</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>-2.68333811479964</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>-1.204216170276561</v>
+      </c>
+      <c r="F8" s="6" t="inlineStr"/>
+      <c r="G8" s="6" t="inlineStr"/>
+      <c r="H8" s="6" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>-2,56; 0,0</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 2,46</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 1,58</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>0.966102981803685</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>-0.25501014458375</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>0.5289654534200686</v>
+      </c>
+      <c r="F9" s="6" t="inlineStr"/>
+      <c r="G9" s="6" t="inlineStr"/>
+      <c r="H9" s="6" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>12-15</t>
+          <t>8-11</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -834,34 +737,26 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>0,36</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>-1,02</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>0,89</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>105,43%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-72,5%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
+      <c r="C10" s="5" t="n">
+        <v>-0.5089105344748861</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>0.4423556470209574</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>0.3177016495811991</v>
+      </c>
+      <c r="F10" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="G10" s="6" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="H10" s="6" t="inlineStr">
+        <is>
+          <t>inf</t>
         </is>
       </c>
     </row>
@@ -869,122 +764,192 @@
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>-0,66; 2,07</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>-3,44; 0,39</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 3,18</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>-2.564385489924873</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" s="6" t="inlineStr"/>
+      <c r="G11" s="6" t="inlineStr"/>
+      <c r="H11" s="6" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>2.464473563413261</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>1.576894315017044</v>
+      </c>
+      <c r="F12" s="6" t="inlineStr"/>
+      <c r="G12" s="6" t="inlineStr"/>
+      <c r="H12" s="6" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>12-15</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>0.3554807658825816</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>-1.016486436480319</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>0.8868158962726996</v>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>1.054301305227062</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>-0.7249607469224855</v>
+      </c>
+      <c r="H13" s="6" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>-0.6559607840497612</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>-3.43812752966338</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" s="6" t="inlineStr"/>
+      <c r="G14" s="6" t="inlineStr"/>
+      <c r="H14" s="6" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>2.070018360815443</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>0.385487894270663</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>3.18388263101118</v>
+      </c>
+      <c r="F15" s="6" t="inlineStr"/>
+      <c r="G15" s="6" t="inlineStr"/>
+      <c r="H15" s="6" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>0,08</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>-0,6</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>0,11</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>26,83%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>-75,82%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>41,39%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>-0,4; 0,56</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>-1,3; -0,07</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>-0,35; 0,66</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; —</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; 17,22</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="C16" s="5" t="n">
+        <v>0.07795791462623849</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>-0.5967358682076134</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>0.1110770308573143</v>
+      </c>
+      <c r="F16" s="6" t="n">
+        <v>0.2682880010347365</v>
+      </c>
+      <c r="G16" s="6" t="n">
+        <v>-0.7581551860745442</v>
+      </c>
+      <c r="H16" s="6" t="n">
+        <v>0.4138745132289368</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>-0.4008567856502289</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>-1.304633574010192</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>-0.3488365167655252</v>
+      </c>
+      <c r="F17" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="G17" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H17" s="6" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>0.562622919297562</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>-0.06708940416634654</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>0.6565341321135393</v>
+      </c>
+      <c r="F18" s="6" t="inlineStr"/>
+      <c r="G18" s="6" t="n">
+        <v>0.1721850036465662</v>
+      </c>
+      <c r="H18" s="6" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -993,13 +958,13 @@
   </sheetData>
   <mergeCells count="8">
     <mergeCell ref="C1:E1"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="F1:H1"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
